--- a/bancos/manual/desc_subfuncao.xlsx
+++ b/bancos/manual/desc_subfuncao.xlsx
@@ -1580,4 +1580,273 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010070B48C6A71B58C48A22499B3FBD0C5AB" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bf68d2055ec0b0618b2600d8294280b1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ad1a0d50-b04c-47c2-aecf-ce05d35f4ea1" xmlns:ns3="9130dfcb-b4a9-4659-a000-3866fb0c64c6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13deb1c62df883ac8433d4d19ab41b31" ns2:_="" ns3:_="">
+    <xsd:import namespace="ad1a0d50-b04c-47c2-aecf-ce05d35f4ea1"/>
+    <xsd:import namespace="9130dfcb-b4a9-4659-a000-3866fb0c64c6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ad1a0d50-b04c-47c2-aecf-ce05d35f4ea1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="12" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9130dfcb-b4a9-4659-a000-3866fb0c64c6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="13" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="14" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{04bcee71-260e-4af6-8c91-84ac34d67b58}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9130dfcb-b4a9-4659-a000-3866fb0c64c6">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9130dfcb-b4a9-4659-a000-3866fb0c64c6" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ad1a0d50-b04c-47c2-aecf-ce05d35f4ea1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F3A2505-A1C2-441B-B398-0C89EB7C2D27}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB213760-831D-44B4-8BD0-1FB7EEED6F65}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95EC47E8-0B4E-4646-AEF3-B5240E5E078B}"/>
 </file>
--- a/bancos/manual/desc_subfuncao.xlsx
+++ b/bancos/manual/desc_subfuncao.xlsx
@@ -1583,8 +1583,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e1f47f591d2cee6122bef25da059db4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="856a76bd91320367711680b85ef754cf" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="17" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="c170a06b81d8b923cbfe6a63de8ee1c9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="844dfdedaab7989660d9d802f918fcda" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1663,7 +1663,7 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="917d32f3-4fa4-4f5b-a8d0-62dbd3d265b9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1694,7 +1694,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1713,7 +1713,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -1741,8 +1741,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1847,18 +1847,26 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="6f4338ef-addb-4c87-aefe-1895241b335f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B55B84A-22BB-41B7-A4F7-FF013B0091D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC7D3446-E305-4608-9FB3-21BDE35FB24E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB213760-831D-44B4-8BD0-1FB7EEED6F65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EAA5A96-60E0-4C51-8584-699CBD88CF93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95EC47E8-0B4E-4646-AEF3-B5240E5E078B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
 </file>
--- a/bancos/manual/desc_subfuncao.xlsx
+++ b/bancos/manual/desc_subfuncao.xlsx
@@ -1583,8 +1583,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="17" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="c170a06b81d8b923cbfe6a63de8ee1c9">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="844dfdedaab7989660d9d802f918fcda" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1b889f39a240c2e855286b20cf95d05e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="902f44b668f40cdc6ccc2fe791adf365" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1609,6 +1609,7 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1688,6 +1689,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1854,13 +1860,12 @@
         <AccountType/>
       </UserInfo>
     </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="6f4338ef-addb-4c87-aefe-1895241b335f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC7D3446-E305-4608-9FB3-21BDE35FB24E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{280E4225-92D5-404F-B29B-78FD7F2EE672}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/bancos/manual/desc_subfuncao.xlsx
+++ b/bancos/manual/desc_subfuncao.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29301"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\2.Programação e Normas\2023\PPAG 2023 e LOA 2023\Tabelas de Apoio - geração dos volumes 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EC26C91BF040C27A188F7B201667BB70E4AC1C1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="3645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -249,6 +250,9 @@
     <t>DIFUSÃO DO CONHECIMENTO CIENTÍFICO E TECNOLÓGICO</t>
   </si>
   <si>
+    <t>ABASTECIMENTO</t>
+  </si>
+  <si>
     <t>EXTENSÃO RURAL</t>
   </si>
   <si>
@@ -361,16 +365,13 @@
   </si>
   <si>
     <t>RESERVA DE CONTINGÊNCIA</t>
-  </si>
-  <si>
-    <t>ABASTECIMENTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,15 +681,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -696,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>31</v>
       </c>
@@ -704,7 +705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>32</v>
       </c>
@@ -712,7 +713,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>61</v>
       </c>
@@ -720,7 +721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>62</v>
       </c>
@@ -728,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>91</v>
       </c>
@@ -736,7 +737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>92</v>
       </c>
@@ -744,7 +745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>121</v>
       </c>
@@ -752,7 +753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>122</v>
       </c>
@@ -760,7 +761,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>123</v>
       </c>
@@ -768,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>124</v>
       </c>
@@ -776,7 +777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>125</v>
       </c>
@@ -784,7 +785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>126</v>
       </c>
@@ -792,7 +793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>127</v>
       </c>
@@ -800,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>128</v>
       </c>
@@ -808,7 +809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>129</v>
       </c>
@@ -816,7 +817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>130</v>
       </c>
@@ -824,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>131</v>
       </c>
@@ -832,7 +833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>151</v>
       </c>
@@ -840,7 +841,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>152</v>
       </c>
@@ -848,7 +849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>153</v>
       </c>
@@ -856,7 +857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>181</v>
       </c>
@@ -864,7 +865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>182</v>
       </c>
@@ -872,7 +873,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>183</v>
       </c>
@@ -880,7 +881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>211</v>
       </c>
@@ -888,7 +889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>212</v>
       </c>
@@ -896,7 +897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>241</v>
       </c>
@@ -904,7 +905,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>242</v>
       </c>
@@ -912,7 +913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>243</v>
       </c>
@@ -920,7 +921,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>244</v>
       </c>
@@ -928,7 +929,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>271</v>
       </c>
@@ -936,7 +937,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>272</v>
       </c>
@@ -944,7 +945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>273</v>
       </c>
@@ -952,7 +953,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>274</v>
       </c>
@@ -960,7 +961,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>301</v>
       </c>
@@ -968,7 +969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>302</v>
       </c>
@@ -976,7 +977,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>303</v>
       </c>
@@ -984,7 +985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>304</v>
       </c>
@@ -992,7 +993,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>305</v>
       </c>
@@ -1000,7 +1001,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>306</v>
       </c>
@@ -1008,7 +1009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="A41">
         <v>331</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="A42">
         <v>332</v>
       </c>
@@ -1024,7 +1025,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2">
       <c r="A43">
         <v>333</v>
       </c>
@@ -1032,7 +1033,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44">
         <v>334</v>
       </c>
@@ -1040,7 +1041,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45">
         <v>361</v>
       </c>
@@ -1048,7 +1049,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46">
         <v>362</v>
       </c>
@@ -1056,7 +1057,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2">
       <c r="A47">
         <v>363</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48">
         <v>364</v>
       </c>
@@ -1072,7 +1073,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="A49">
         <v>365</v>
       </c>
@@ -1080,7 +1081,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2">
       <c r="A50">
         <v>366</v>
       </c>
@@ -1088,7 +1089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2">
       <c r="A51">
         <v>367</v>
       </c>
@@ -1096,7 +1097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2">
       <c r="A52">
         <v>368</v>
       </c>
@@ -1104,7 +1105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2">
       <c r="A53">
         <v>391</v>
       </c>
@@ -1112,7 +1113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2">
       <c r="A54">
         <v>392</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2">
       <c r="A55">
         <v>421</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2">
       <c r="A56">
         <v>422</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2">
       <c r="A57">
         <v>423</v>
       </c>
@@ -1144,7 +1145,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2">
       <c r="A58">
         <v>451</v>
       </c>
@@ -1152,7 +1153,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2">
       <c r="A59">
         <v>452</v>
       </c>
@@ -1160,7 +1161,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2">
       <c r="A60">
         <v>453</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2">
       <c r="A61">
         <v>481</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2">
       <c r="A62">
         <v>482</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2">
       <c r="A63">
         <v>511</v>
       </c>
@@ -1192,7 +1193,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2">
       <c r="A64">
         <v>512</v>
       </c>
@@ -1200,7 +1201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>541</v>
       </c>
@@ -1208,7 +1209,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>542</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>543</v>
       </c>
@@ -1224,7 +1225,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>544</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>545</v>
       </c>
@@ -1240,7 +1241,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>571</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>572</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>573</v>
       </c>
@@ -1264,316 +1265,316 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>605</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>606</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>607</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>608</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>609</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>631</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>632</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>661</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81">
         <v>662</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82">
         <v>663</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83">
         <v>664</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84">
         <v>665</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85">
         <v>691</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86">
         <v>692</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87">
         <v>693</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88">
         <v>694</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89">
         <v>695</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90">
         <v>721</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91">
         <v>722</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92">
         <v>751</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93">
         <v>752</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94">
         <v>753</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95">
         <v>754</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96">
         <v>781</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97">
         <v>782</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98">
         <v>783</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99">
         <v>784</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100">
         <v>785</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101">
         <v>811</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102">
         <v>812</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103">
         <v>813</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104">
         <v>841</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105">
         <v>842</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106">
         <v>843</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107">
         <v>844</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108">
         <v>845</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109">
         <v>846</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110">
         <v>847</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111">
         <v>999</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1583,8 +1584,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1b889f39a240c2e855286b20cf95d05e">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="902f44b668f40cdc6ccc2fe791adf365" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08D58FADB61F04EBBB4F355C06EFBED" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7797dc5feb179b4da55a9ebddd321181">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f4338ef-addb-4c87-aefe-1895241b335f" xmlns:ns3="b91e7f20-fe0a-487d-91a9-605ac1c64acf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90078f443198b6d5c0fd169535a443b9" ns2:_="" ns3:_="">
     <xsd:import namespace="6f4338ef-addb-4c87-aefe-1895241b335f"/>
     <xsd:import namespace="b91e7f20-fe0a-487d-91a9-605ac1c64acf"/>
     <xsd:element name="properties">
@@ -1610,6 +1638,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1692,6 +1721,11 @@
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -1837,35 +1871,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f4338ef-addb-4c87-aefe-1895241b335f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="b91e7f20-fe0a-487d-91a9-605ac1c64acf">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{280E4225-92D5-404F-B29B-78FD7F2EE672}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1873,5 +1880,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A8736FE-6255-4FD1-8C32-47721AF24FF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60504B4E-13D0-4AB7-834B-C4A00410F540}"/>
 </file>